--- a/public/exports-with-coowners/29189595.xlsx
+++ b/public/exports-with-coowners/29189595.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">

--- a/public/exports-with-coowners/29189595.xlsx
+++ b/public/exports-with-coowners/29189595.xlsx
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 11</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J139">
-        <v>5120</v>
+        <v>798</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558253</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,30 +10466,30 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 13</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J140">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558254</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,30 +10541,30 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elise Sørensens Vej 2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">1352997</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>431</v>
+        <v>1771</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558244</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elledevej 59</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">2459947</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J142">
-        <v>3294</v>
+        <v>2103</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558263</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Rynkevangen 14C</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5342669</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J143">
-        <v>1326</v>
+        <v>980</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558264</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Torvet 3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5341684</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>408</v>
+        <v>1510</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558248</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Hyldens Kvarter 1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,30 +10851,30 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100430393, 100430394</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>754</v>
+        <v>532</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311562890</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10901,12 +10901,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 27</t>
+          <t xml:space="preserve">Hyldens Kvarter 3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,30 +10926,30 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100430393, 100430394</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>341</v>
+        <v>742</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311562889</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -10991,40 +10991,40 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Hyldens Kvarter 7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">100430393, 100430394</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J147">
-        <v>798</v>
+        <v>596</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558253</t>
+          <t xml:space="preserve">311562886</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,40 +11066,40 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Hyldens Kvarter 9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">100430394, 100562924</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J148">
-        <v>683</v>
+        <v>593</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558254</t>
+          <t xml:space="preserve">311562885</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elise Sørensens Vej 2</t>
+          <t xml:space="preserve">Herredsåsen 23</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,30 +11151,30 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352997</t>
+          <t xml:space="preserve">276426, 276427</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>1771</v>
+        <v>1278</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558244</t>
+          <t xml:space="preserve">311576824</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-02-04</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11201,12 +11201,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledevej 59</t>
+          <t xml:space="preserve">Kåstrupvej 45</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,30 +11226,30 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459947</t>
+          <t xml:space="preserve">276435, 276436</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>2103</v>
+        <v>888</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558263</t>
+          <t xml:space="preserve">311582746</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11276,12 +11276,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rynkevangen 14C</t>
+          <t xml:space="preserve">Klostermosen 1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,30 +11301,30 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342669</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J151">
-        <v>980</v>
+        <v>287</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558264</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 3</t>
+          <t xml:space="preserve">Klostermosen 2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,30 +11376,30 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341684</t>
+          <t xml:space="preserve">275985</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J152">
-        <v>1510</v>
+        <v>414</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558248</t>
+          <t xml:space="preserve">311586360</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,40 +11441,40 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 1</t>
+          <t xml:space="preserve">Klostermosen 33</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430393, 100430394</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>532</v>
+        <v>854</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562890</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,40 +11516,40 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 3</t>
+          <t xml:space="preserve">Klostermosen 57</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430393, 100430394</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>742</v>
+        <v>854</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562889</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,40 +11591,40 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 7</t>
+          <t xml:space="preserve">Klostermosen 9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430393, 100430394</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J155">
-        <v>596</v>
+        <v>854</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562886</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,40 +11666,40 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 9</t>
+          <t xml:space="preserve">Centret 9</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4470</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430394, 100562924</t>
+          <t xml:space="preserve">9921582</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562885</t>
+          <t xml:space="preserve">311594043</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -11741,40 +11741,40 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsåsen 23</t>
+          <t xml:space="preserve">Odinsvej 20</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">276426, 276427</t>
+          <t xml:space="preserve">2472174</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>1278</v>
+        <v>2864</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576824</t>
+          <t xml:space="preserve">311617056</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-04</t>
+          <t xml:space="preserve">2032-07-26</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kåstrupvej 45</t>
+          <t xml:space="preserve">Bredgade 26</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">276435, 276436</t>
+          <t xml:space="preserve">5341470</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,21 +11835,21 @@
         </is>
       </c>
       <c r="J158">
-        <v>888</v>
+        <v>1011</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582746</t>
+          <t xml:space="preserve">311620368</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-04</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 1</t>
+          <t xml:space="preserve">Melbygade 2B</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,30 +11901,30 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">2459072</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311620364</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 2</t>
+          <t xml:space="preserve">Radiovej 1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,30 +11976,30 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">275985</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J160">
-        <v>414</v>
+        <v>252</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586360</t>
+          <t xml:space="preserve">311620792</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 33</t>
+          <t xml:space="preserve">Radiovej 5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,30 +12051,30 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J161">
-        <v>854</v>
+        <v>486</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311620791</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12101,12 +12101,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 57</t>
+          <t xml:space="preserve">Algade 14</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">2474884</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,21 +12135,21 @@
         </is>
       </c>
       <c r="J162">
-        <v>854</v>
+        <v>357</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311622694</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 9</t>
+          <t xml:space="preserve">Langagervej 15</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,30 +12201,30 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">5343581</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>854</v>
+        <v>653</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311622692</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,40 +12266,40 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centret 9</t>
+          <t xml:space="preserve">Omfartsvejen 5</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4470</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9921582</t>
+          <t xml:space="preserve">7544797</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J164">
-        <v>633</v>
+        <v>403</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594043</t>
+          <t xml:space="preserve">311622697</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-21</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 20</t>
+          <t xml:space="preserve">Røsnæsvej 225</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472174</t>
+          <t xml:space="preserve">7761346</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,21 +12360,21 @@
         </is>
       </c>
       <c r="J165">
-        <v>2864</v>
+        <v>350</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617056</t>
+          <t xml:space="preserve">311622695</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-26</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 26</t>
+          <t xml:space="preserve">Græsmarken 19B</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341470</t>
+          <t xml:space="preserve">8316898</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>1011</v>
+        <v>362</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620368</t>
+          <t xml:space="preserve">311629060</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbygade 2B</t>
+          <t xml:space="preserve">Stadion Alle 13</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459072</t>
+          <t xml:space="preserve">8116851</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J167">
-        <v>308</v>
+        <v>709</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620364</t>
+          <t xml:space="preserve">311629056</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Munkesøparken</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 1</t>
+          <t xml:space="preserve">Esbern Snaresvej 57</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,30 +12576,30 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">276009, 276010</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>252</v>
+        <v>2341</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620792</t>
+          <t xml:space="preserve">311631835</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-09-28</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">FÆLLESORG BOLIGFORENING</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 5</t>
+          <t xml:space="preserve">Frederik Andersensvej 31</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,30 +12651,30 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">420517, 420518</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J169">
-        <v>486</v>
+        <v>2606</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620791</t>
+          <t xml:space="preserve">311669777</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -12716,17 +12716,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 14</t>
+          <t xml:space="preserve">Røsnæsvej 69C</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2474884</t>
+          <t xml:space="preserve">276422, 276423</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,21 +12735,21 @@
         </is>
       </c>
       <c r="J170">
-        <v>357</v>
+        <v>1980</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622694</t>
+          <t xml:space="preserve">311674759</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12776,12 +12776,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langagervej 15</t>
+          <t xml:space="preserve">Røsnæsvej 69D</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,30 +12801,30 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5343581</t>
+          <t xml:space="preserve">276422, 276423</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J171">
-        <v>653</v>
+        <v>2054</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622692</t>
+          <t xml:space="preserve">311674738</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,40 +12866,40 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omfartsvejen 5</t>
+          <t xml:space="preserve">Røsnæsvej 69B</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7544797</t>
+          <t xml:space="preserve">276423</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J172">
-        <v>403</v>
+        <v>1452</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622697</t>
+          <t xml:space="preserve">311677823</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-05-02</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 225</t>
+          <t xml:space="preserve">Lerchenfeldvej 34</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7761346</t>
+          <t xml:space="preserve">275085, 275086, 275087</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="J173">
-        <v>350</v>
+        <v>1849</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622695</t>
+          <t xml:space="preserve">311722596</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græsmarken 19B</t>
+          <t xml:space="preserve">Enggårdsvej 5A</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4490</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316898</t>
+          <t xml:space="preserve">276464, 276465, 276466</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,21 +13035,21 @@
         </is>
       </c>
       <c r="J174">
-        <v>362</v>
+        <v>3536</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629060</t>
+          <t xml:space="preserve">311774253</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2034-07-19</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 13</t>
+          <t xml:space="preserve">Frederik Andersensvej 1</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,30 +13101,30 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116851</t>
+          <t xml:space="preserve">5342092</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J175">
-        <v>709</v>
+        <v>395</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629056</t>
+          <t xml:space="preserve">311803915</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2034-12-20</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Munkesøparken</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -13166,40 +13166,40 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esbern Snaresvej 57</t>
+          <t xml:space="preserve">Rosenvænget 11</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">276009, 276010</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J176">
-        <v>2341</v>
+        <v>5120</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311631835</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-28</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13226,12 +13226,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">FÆLLESORG BOLIGFORENING</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -13241,40 +13241,40 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Andersensvej 31</t>
+          <t xml:space="preserve">Rosenvænget 13</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">420517, 420518</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J177">
-        <v>2606</v>
+        <v>682</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669777</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -13316,40 +13316,40 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69C</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">276422, 276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J178">
-        <v>1980</v>
+        <v>431</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674759</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -13391,17 +13391,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69D</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">276422, 276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,21 +13410,21 @@
         </is>
       </c>
       <c r="J179">
-        <v>2054</v>
+        <v>3294</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674738</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,40 +13466,40 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69B</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J180">
-        <v>1452</v>
+        <v>1326</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677823</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-02</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -13541,40 +13541,40 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerchenfeldvej 34</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">275085, 275086, 275087</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J181">
-        <v>1849</v>
+        <v>408</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722596</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-15</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13601,12 +13601,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -13616,40 +13616,40 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggårdsvej 5A</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">276464, 276465, 276466</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J182">
-        <v>3536</v>
+        <v>754</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311774253</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,40 +13691,40 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Andersensvej 1</t>
+          <t xml:space="preserve">Rosenvænget 27</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342092</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J183">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803915</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-20</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
